--- a/data/trans_dic/P39A4_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,99; 93,62</t>
+          <t>81,15; 93,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,17; 95,91</t>
+          <t>87,1; 95,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,11; 93,52</t>
+          <t>85,13; 93,54</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,42; 96,12</t>
+          <t>89,28; 96,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,78; 94,07</t>
+          <t>44,32; 94,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,81; 93,96</t>
+          <t>64,95; 93,84</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,94; 95,62</t>
+          <t>91,27; 95,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,25; 95,09</t>
+          <t>91,55; 95,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,97; 94,79</t>
+          <t>92,11; 94,94</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>93,28; 98,37</t>
+          <t>93,47; 98,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,01; 94,17</t>
+          <t>91,01; 94,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,91; 96,62</t>
+          <t>92,9; 96,73</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,34; 93,9</t>
+          <t>89,56; 93,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,41; 96,19</t>
+          <t>93,16; 96,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,95; 94,57</t>
+          <t>91,91; 94,54</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,94; 94,57</t>
+          <t>89,87; 94,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,51; 98,41</t>
+          <t>92,39; 98,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,28; 97,22</t>
+          <t>92,22; 97,11</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>85,85; 92,0</t>
+          <t>85,49; 91,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,46; 92,06</t>
+          <t>87,32; 91,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,54; 91,36</t>
+          <t>87,77; 91,37</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,53; 94,55</t>
+          <t>91,62; 94,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83,21; 93,75</t>
+          <t>84,46; 93,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,25; 93,4</t>
+          <t>88,71; 93,49</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>285105; 329544</t>
+          <t>285670; 329818</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>239637; 263666</t>
+          <t>239453; 263638</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>533582; 586326</t>
+          <t>533692; 586435</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>349338; 375498</t>
+          <t>348760; 376769</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>249720; 462599</t>
+          <t>217947; 463028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>545436; 829094</t>
+          <t>573126; 828022</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>471460; 495725</t>
+          <t>473210; 495486</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>477036; 497131</t>
+          <t>478641; 496901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>957608; 987030</t>
+          <t>959055; 988560</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>801696; 845464</t>
+          <t>803353; 846258</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>597138; 617879</t>
+          <t>597108; 618223</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1408108; 1464310</t>
+          <t>1408007; 1465991</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>473872; 498058</t>
+          <t>475020; 497680</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>488156; 502659</t>
+          <t>486855; 501756</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>968177; 995840</t>
+          <t>967751; 995533</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>305851; 321621</t>
+          <t>305623; 321112</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>534230; 568265</t>
+          <t>533509; 567257</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>846656; 892059</t>
+          <t>846176; 890971</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>213356; 228634</t>
+          <t>212471; 228310</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>305574; 321663</t>
+          <t>305090; 321192</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>523436; 546275</t>
+          <t>524780; 546344</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2965068; 3063135</t>
+          <t>2968242; 3063766</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2824859; 3182742</t>
+          <t>2867313; 3185179</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5855033; 6196508</t>
+          <t>5885563; 6202989</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A4_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,15; 93,7</t>
+          <t>81,06; 93,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,1; 95,9</t>
+          <t>86,66; 94,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,13; 93,54</t>
+          <t>85,3; 92,98</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,28; 96,45</t>
+          <t>89,63; 96,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,32; 94,16</t>
+          <t>89,45; 94,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,95; 93,84</t>
+          <t>90,89; 94,89</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,27; 95,57</t>
+          <t>90,29; 94,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,55; 95,05</t>
+          <t>90,45; 94,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,11; 94,94</t>
+          <t>91,03; 93,98</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>93,47; 98,46</t>
+          <t>91,01; 95,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,01; 94,22</t>
+          <t>90,63; 93,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,9; 96,73</t>
+          <t>91,42; 93,94</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,56; 93,83</t>
+          <t>88,9; 93,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,16; 96,01</t>
+          <t>92,68; 95,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,91; 94,54</t>
+          <t>91,53; 94,13</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,87; 94,42</t>
+          <t>89,69; 94,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,39; 98,23</t>
+          <t>90,29; 94,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,22; 97,11</t>
+          <t>90,84; 93,83</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>85,49; 91,87</t>
+          <t>85,31; 91,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,32; 91,93</t>
+          <t>86,47; 91,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,77; 91,37</t>
+          <t>86,76; 90,78</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,62; 94,57</t>
+          <t>90,75; 93,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>84,46; 93,82</t>
+          <t>91,47; 93,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,71; 93,49</t>
+          <t>91,33; 92,76</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>311136</t>
+          <t>306635</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>254017</t>
+          <t>289333</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>565152</t>
+          <t>595968</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>285670; 329818</t>
+          <t>281927; 324561</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>239453; 263638</t>
+          <t>274205; 300583</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>533692; 586435</t>
+          <t>566553; 617591</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>364367</t>
+          <t>410156</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>393627</t>
+          <t>435824</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>757994</t>
+          <t>845980</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>348760; 376769</t>
+          <t>393144; 423262</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>217947; 463028</t>
+          <t>421048; 446427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>573126; 828022</t>
+          <t>826514; 862894</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>486065</t>
+          <t>543211</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>488335</t>
+          <t>549661</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>974400</t>
+          <t>1092870</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>473210; 495486</t>
+          <t>528509; 555934</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>478641; 496901</t>
+          <t>537492; 560062</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>959055; 988560</t>
+          <t>1073720; 1108558</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>823410</t>
+          <t>619021</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>608025</t>
+          <t>653676</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1431434</t>
+          <t>1272697</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>803353; 846258</t>
+          <t>603277; 631255</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>597108; 618223</t>
+          <t>641826; 664565</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1408007; 1465991</t>
+          <t>1253409; 1287918</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>487250</t>
+          <t>522450</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>495658</t>
+          <t>545837</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>982908</t>
+          <t>1068287</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>475020; 497680</t>
+          <t>507405; 534206</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>486855; 501756</t>
+          <t>536664; 554147</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>967751; 995533</t>
+          <t>1052403; 1082337</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>314298</t>
+          <t>346176</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>551443</t>
+          <t>375262</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>865741</t>
+          <t>721439</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>305623; 321112</t>
+          <t>336703; 354748</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>533509; 567257</t>
+          <t>366131; 382523</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>846176; 890971</t>
+          <t>709384; 732699</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>221729</t>
+          <t>243194</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>313958</t>
+          <t>340489</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>535688</t>
+          <t>583683</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>212471; 228310</t>
+          <t>233447; 251398</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>305090; 321192</t>
+          <t>330582; 348862</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>524780; 546344</t>
+          <t>569074; 595469</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3008256</t>
+          <t>2990841</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3105063</t>
+          <t>3190083</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6113319</t>
+          <t>6180923</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2968242; 3063766</t>
+          <t>2953393; 3027169</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2867313; 3185179</t>
+          <t>3161598; 3217929</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5885563; 6202989</t>
+          <t>6128895; 6224926</t>
         </is>
       </c>
     </row>
